--- a/TestCase/Zerobank_login.xlsx
+++ b/TestCase/Zerobank_login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SDET_Wipro\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7C5779-FF4A-4309-81E4-50012D8015F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2EFE12-D83D-433B-B172-93951376E141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A5FC55C4-F918-4E26-8E4B-33108ED72930}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>Zerobank login page</t>
   </si>
@@ -285,6 +285,36 @@
   </si>
   <si>
     <t>4. Verify Login button shows validation for empty fields</t>
+  </si>
+  <si>
+    <t>Verify Sign in button</t>
+  </si>
+  <si>
+    <t>1. Verify Sign in button is visible on login page</t>
+  </si>
+  <si>
+    <t>2. Verify Sign in button is clickable</t>
+  </si>
+  <si>
+    <t>3. Verify Sign in button redirects user after valid login</t>
+  </si>
+  <si>
+    <t>4. Verify Sign in button shows error for invalid credentials</t>
+  </si>
+  <si>
+    <t>5. Verify Sign in button shows validation when fields are empty</t>
+  </si>
+  <si>
+    <t>Verify Forgot password link</t>
+  </si>
+  <si>
+    <t>1. Verify Forgot password link is visible</t>
+  </si>
+  <si>
+    <t>2. Verify Forgot password link is clickable</t>
+  </si>
+  <si>
+    <t>3. Verify Forgot password link redirects to password recovery page</t>
   </si>
 </sst>
 </file>
@@ -685,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26525677-3292-4A6B-891E-45F48728528A}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -946,6 +976,82 @@
       </c>
       <c r="C30" s="8" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18" customHeight="1">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
